--- a/TDXapp/tdxAppData/tdxIndexsBLK.xlsx
+++ b/TDXapp/tdxAppData/tdxIndexsBLK.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E653"/>
+  <dimension ref="A1:E588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1010</v>
+        <v>1066</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>155</v>
+        <v>92</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1358,12 +1358,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>880842</t>
+          <t>880854</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>业绩预升</t>
+          <t>预高送转</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1383,12 +1383,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>880619</t>
+          <t>880851</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>业绩预增</t>
+          <t>已高送转</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1408,12 +1408,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>880843</t>
+          <t>880842</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>业绩预降</t>
+          <t>业绩预升</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>388</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1433,12 +1433,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>880844</t>
+          <t>880619</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>预计扭亏</t>
+          <t>业绩预增</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1458,12 +1458,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>880825</t>
+          <t>880846</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>预计转亏</t>
+          <t>破净资产</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1483,12 +1483,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>880846</t>
+          <t>880891</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>破净资产</t>
+          <t>破发行价</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>444</v>
+        <v>203</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1508,12 +1508,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>880891</t>
+          <t>880622</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>破发行价</t>
+          <t>破增发价</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>302</v>
+        <v>64</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1533,12 +1533,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>880622</t>
+          <t>880845</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>破增发价</t>
+          <t>高股息股</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>880845</t>
+          <t>880526</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>高股息股</t>
+          <t>高分红股</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1583,12 +1583,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>880526</t>
+          <t>880763</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>高分红股</t>
+          <t>自由现金流</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>353</v>
+        <v>200</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>767</v>
+        <v>965</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>674</v>
+        <v>579</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>251</v>
+        <v>444</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>159</v>
+        <v>406</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>267</v>
+        <v>199</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3983,12 +3983,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>880665</t>
+          <t>880812</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>昨ST首板</t>
+          <t>昨日连板</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4008,12 +4008,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>880812</t>
+          <t>880556</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>昨日连板</t>
+          <t>昨ST连板</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4033,12 +4033,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>880556</t>
+          <t>880886</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>昨ST连板</t>
+          <t>昨日较强</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4058,12 +4058,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>880886</t>
+          <t>880784</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>昨日较强</t>
+          <t>昨日较弱</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4083,12 +4083,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>880784</t>
+          <t>880864</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>昨日较弱</t>
+          <t>昨日振荡</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4108,12 +4108,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>880864</t>
+          <t>880690</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>昨日振荡</t>
+          <t>昨日强势</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4133,12 +4133,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>880690</t>
+          <t>880691</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>昨日强势</t>
+          <t>昨日弱势</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4158,12 +4158,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>880691</t>
+          <t>880770</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>昨日弱势</t>
+          <t>昨日上榜</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4183,12 +4183,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>880770</t>
+          <t>880867</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>昨日上榜</t>
+          <t>昨高换手</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4208,12 +4208,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>880867</t>
+          <t>880789</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>昨高换手</t>
+          <t>昨成交20</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4233,12 +4233,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>880789</t>
+          <t>880822</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>昨成交20</t>
+          <t>昨收活跃</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>880822</t>
+          <t>880915</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>昨收活跃</t>
+          <t>昨日突涨</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>最近情绪</t>
+          <t>最近情绪指数</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>570</v>
+        <v>675</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>铁路基建</t>
+          <t>高铁</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>206</v>
+        <v>269</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>394</v>
+        <v>837</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>384</v>
+        <v>469</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>456</v>
+        <v>680</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>736</v>
+        <v>934</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>255</v>
+        <v>361</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>692</v>
+        <v>820</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>111</v>
+        <v>226</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>车路云</t>
+          <t>车联网</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>64</v>
+        <v>285</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -11583,21 +11583,21 @@
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
         <is>
-          <t>881002</t>
+          <t>880732</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>AI智能体</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -11608,21 +11608,21 @@
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
         <is>
-          <t>881005</t>
+          <t>880978</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>焦炭加工</t>
+          <t>DeepSeek概念</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>8</v>
+        <v>665</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
     <row r="449">
       <c r="A449" s="1" t="inlineStr">
         <is>
-          <t>881007</t>
+          <t>880747</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>油气开采</t>
+          <t>AI医疗概念</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
@@ -11658,21 +11658,21 @@
     <row r="450">
       <c r="A450" s="1" t="inlineStr">
         <is>
-          <t>881011</t>
+          <t>880765</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>海洋经济</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -11683,21 +11683,21 @@
     <row r="451">
       <c r="A451" s="1" t="inlineStr">
         <is>
-          <t>881008</t>
+          <t>880912</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>油服工程</t>
+          <t>外骨骼机器人</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -11708,21 +11708,21 @@
     <row r="452">
       <c r="A452" s="1" t="inlineStr">
         <is>
-          <t>881016</t>
+          <t>880914</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>日用化工</t>
+          <t>军贸概念</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>概念</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -11733,12 +11733,12 @@
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
         <is>
-          <t>881019</t>
+          <t>880301</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -11747,7 +11747,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -11758,12 +11758,12 @@
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
         <is>
-          <t>881026</t>
+          <t>880305</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>化学原料</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -11783,12 +11783,12 @@
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
         <is>
-          <t>881034</t>
+          <t>880310</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -11808,12 +11808,12 @@
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t>881044</t>
+          <t>880318</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -11833,12 +11833,12 @@
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
         <is>
-          <t>881051</t>
+          <t>880324</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>橡胶</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -11858,12 +11858,12 @@
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
         <is>
-          <t>881055</t>
+          <t>880330</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>农用化工</t>
+          <t>化纤</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -11883,12 +11883,12 @@
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
         <is>
-          <t>881104</t>
+          <t>880335</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>非金属材料</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>17</v>
+        <v>436</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -11908,12 +11908,12 @@
     <row r="460">
       <c r="A460" s="1" t="inlineStr">
         <is>
-          <t>881062</t>
+          <t>880344</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>冶钢原料</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -11922,7 +11922,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -11933,12 +11933,12 @@
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
         <is>
-          <t>881065</t>
+          <t>880350</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>造纸</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -11958,12 +11958,12 @@
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t>881069</t>
+          <t>880351</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>特钢</t>
+          <t>矿物制品</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -11983,12 +11983,12 @@
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
         <is>
-          <t>881071</t>
+          <t>880355</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>日用化工</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -12008,12 +12008,12 @@
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
         <is>
-          <t>881075</t>
+          <t>880360</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -12033,12 +12033,12 @@
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t>881078</t>
+          <t>880367</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>能源金属</t>
+          <t>纺织服饰</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -12058,12 +12058,12 @@
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t>881082</t>
+          <t>880372</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -12072,7 +12072,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -12083,12 +12083,12 @@
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t>881087</t>
+          <t>880380</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>金属新材料</t>
+          <t>酿酒</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -12108,12 +12108,12 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t>881091</t>
+          <t>880387</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>家用电器</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -12133,12 +12133,12 @@
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
         <is>
-          <t>881094</t>
+          <t>880390</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>玻璃玻纤</t>
+          <t>汽车类</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -12147,7 +12147,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>16</v>
+        <v>291</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -12158,12 +12158,12 @@
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
         <is>
-          <t>881097</t>
+          <t>880398</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>装饰建材</t>
+          <t>医疗保健</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -12183,12 +12183,12 @@
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
         <is>
-          <t>881106</t>
+          <t>880399</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -12208,12 +12208,12 @@
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
         <is>
-          <t>881111</t>
+          <t>880400</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>养殖业</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -12222,7 +12222,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -12233,12 +12233,12 @@
     <row r="473">
       <c r="A473" s="1" t="inlineStr">
         <is>
-          <t>881115</t>
+          <t>880406</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>林业</t>
+          <t>商业连锁</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -12247,7 +12247,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -12258,12 +12258,12 @@
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
         <is>
-          <t>881116</t>
+          <t>880414</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>渔业</t>
+          <t>商贸代理</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -12283,12 +12283,12 @@
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t>881119</t>
+          <t>880418</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>传媒娱乐</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -12308,12 +12308,12 @@
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t>881123</t>
+          <t>880421</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>广告包装</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -12333,12 +12333,12 @@
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
         <is>
-          <t>881127</t>
+          <t>880422</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>动物保健</t>
+          <t>文教休闲</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -12347,7 +12347,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -12358,12 +12358,12 @@
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
         <is>
-          <t>881130</t>
+          <t>880423</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>酿酒</t>
+          <t>酒店餐饮</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -12383,12 +12383,12 @@
     <row r="479">
       <c r="A479" s="1" t="inlineStr">
         <is>
-          <t>881136</t>
+          <t>880424</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>饮料乳品</t>
+          <t>旅游</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -12408,12 +12408,12 @@
     <row r="480">
       <c r="A480" s="1" t="inlineStr">
         <is>
-          <t>881139</t>
+          <t>880430</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -12433,12 +12433,12 @@
     <row r="481">
       <c r="A481" s="1" t="inlineStr">
         <is>
-          <t>881140</t>
+          <t>880431</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>休闲食品</t>
+          <t>船舶</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -12458,12 +12458,12 @@
     <row r="482">
       <c r="A482" s="1" t="inlineStr">
         <is>
-          <t>881144</t>
+          <t>880432</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>运输设备</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -12483,12 +12483,12 @@
     <row r="483">
       <c r="A483" s="1" t="inlineStr">
         <is>
-          <t>881151</t>
+          <t>880437</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>纺织制造</t>
+          <t>通用机械</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -12508,12 +12508,12 @@
     <row r="484">
       <c r="A484" s="1" t="inlineStr">
         <is>
-          <t>881157</t>
+          <t>880440</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>服装家纺</t>
+          <t>工业机械</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>57</v>
+        <v>319</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -12533,12 +12533,12 @@
     <row r="485">
       <c r="A485" s="1" t="inlineStr">
         <is>
-          <t>881162</t>
+          <t>880446</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>饰品</t>
+          <t>电气设备</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>15</v>
+        <v>327</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -12558,12 +12558,12 @@
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
         <is>
-          <t>881167</t>
+          <t>880447</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>造纸</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -12583,12 +12583,12 @@
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t>881171</t>
+          <t>880448</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>包装印刷</t>
+          <t>电器仪表</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -12608,12 +12608,12 @@
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
         <is>
-          <t>881177</t>
+          <t>880452</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电信运营</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -12633,12 +12633,12 @@
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t>881180</t>
+          <t>880453</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>文娱用品</t>
+          <t>公共交通</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -12658,12 +12658,12 @@
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t>881184</t>
+          <t>880454</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -12683,12 +12683,12 @@
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
         <is>
-          <t>881187</t>
+          <t>880455</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>黑色家电</t>
+          <t>供气供热</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -12708,12 +12708,12 @@
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
         <is>
-          <t>881190</t>
+          <t>880456</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>环境保护</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -12733,12 +12733,12 @@
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
         <is>
-          <t>881194</t>
+          <t>880459</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>厨卫电器</t>
+          <t>运输服务</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -12758,12 +12758,12 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>881198</t>
+          <t>880464</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>家电零部件</t>
+          <t>仓储物流</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -12772,7 +12772,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -12783,12 +12783,12 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>881200</t>
+          <t>880465</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>交通设施</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -12808,12 +12808,12 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>881204</t>
+          <t>880471</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>商业物业经营</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -12833,12 +12833,12 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>881205</t>
+          <t>880472</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>专业连锁</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -12858,12 +12858,12 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>881206</t>
+          <t>880473</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -12883,12 +12883,12 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>881207</t>
+          <t>880474</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>电子商务</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -12897,7 +12897,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -12908,12 +12908,12 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>881212</t>
+          <t>880476</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>乘用车</t>
+          <t>建筑</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -12922,7 +12922,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -12933,12 +12933,12 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>881215</t>
+          <t>880482</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>商用车</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -12958,12 +12958,12 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>881218</t>
+          <t>880489</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>IT设备</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -12983,12 +12983,12 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>881224</t>
+          <t>880490</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>汽车服务</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -13008,12 +13008,12 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>881227</t>
+          <t>880491</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>摩托车及其他</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -13022,7 +13022,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -13033,12 +13033,12 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>881231</t>
+          <t>880492</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>元器件</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -13047,7 +13047,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>136</v>
+        <v>297</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -13058,12 +13058,12 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>881234</t>
+          <t>880493</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>生物制品</t>
+          <t>软件服务</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -13083,12 +13083,12 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>881256</t>
+          <t>880494</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>中药</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -13108,12 +13108,12 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>881252</t>
+          <t>880497</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>综合类</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -13122,7 +13122,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -13133,21 +13133,21 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>881241</t>
+          <t>000300</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>沪深300</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>96</v>
+        <v>300</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -13158,21 +13158,21 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>881247</t>
+          <t>399001</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>医疗服务</t>
+          <t>深证成指</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>54</v>
+        <v>500</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -13183,21 +13183,21 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>881257</t>
+          <t>399006</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>医疗美容</t>
+          <t>创业板指</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -13208,21 +13208,21 @@
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>881261</t>
+          <t>399850</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>电机制造</t>
+          <t>深证50</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -13233,21 +13233,21 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>881262</t>
+          <t>000016</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>电池</t>
+          <t>上证50</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -13258,21 +13258,21 @@
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>881268</t>
+          <t>000688</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>科创50</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>881275</t>
+          <t>899050</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>光伏设备</t>
+          <t>北证50</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -13308,21 +13308,21 @@
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>881282</t>
+          <t>000903</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>风电设备</t>
+          <t>中证A100</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -13333,21 +13333,21 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>881285</t>
+          <t>000510</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>其他发电设备</t>
+          <t>中证A500</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -13358,21 +13358,21 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>881287</t>
+          <t>000905</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>地面兵装</t>
+          <t>中证500</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -13383,21 +13383,21 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>881288</t>
+          <t>000906</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>中证800</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -13408,21 +13408,21 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>881289</t>
+          <t>000852</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>航天装备</t>
+          <t>中证1000</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -13433,21 +13433,21 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>881290</t>
+          <t>399750</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>航海装备</t>
+          <t>深主板50</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -13458,21 +13458,21 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>881291</t>
+          <t>399293</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>军工电子</t>
+          <t>创业大盘</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>881293</t>
+          <t>399673</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>轨交设备</t>
+          <t>创业板50</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -13508,21 +13508,21 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>881294</t>
+          <t>399019</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>创业200</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -13533,21 +13533,21 @@
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>881303</t>
+          <t>399012</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>创业300</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -13558,21 +13558,21 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>881310</t>
+          <t>399020</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>工程机械</t>
+          <t>创业小盘</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -13583,21 +13583,21 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>881313</t>
+          <t>399018</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>创业创新</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -13608,21 +13608,21 @@
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>881319</t>
+          <t>399295</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>创价值</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -13633,21 +13633,21 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>881326</t>
+          <t>399296</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>创成长</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -13658,21 +13658,21 @@
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>881329</t>
+          <t>399269</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>光学光电</t>
+          <t>创质量</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -13683,21 +13683,21 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>881333</t>
+          <t>399276</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>元器件</t>
+          <t>创科技</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
@@ -13708,21 +13708,21 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>881336</t>
+          <t>399275</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>其他电子</t>
+          <t>创医药</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -13733,21 +13733,21 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>881338</t>
+          <t>399372</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>大盘成长</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -13758,21 +13758,21 @@
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
         <is>
-          <t>881347</t>
+          <t>399373</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>大盘价值</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
         <is>
-          <t>881344</t>
+          <t>399374</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>电信服务</t>
+          <t>中盘成长</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -13808,21 +13808,21 @@
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
         <is>
-          <t>881352</t>
+          <t>399375</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>IT设备</t>
+          <t>中盘价值</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -13833,21 +13833,21 @@
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
         <is>
-          <t>881355</t>
+          <t>399376</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>软件服务</t>
+          <t>小盘成长</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>236</v>
+        <v>166</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -13858,21 +13858,21 @@
     <row r="538">
       <c r="A538" s="1" t="inlineStr">
         <is>
-          <t>881359</t>
+          <t>399377</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>云服务</t>
+          <t>小盘价值</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -13883,21 +13883,21 @@
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
         <is>
-          <t>881364</t>
+          <t>000009</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>产业互联网</t>
+          <t>上证380</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>6</v>
+        <v>380</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -13908,21 +13908,21 @@
     <row r="540">
       <c r="A540" s="1" t="inlineStr">
         <is>
-          <t>881369</t>
+          <t>000010</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>上证180</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -13933,21 +13933,21 @@
     <row r="541">
       <c r="A541" s="1" t="inlineStr">
         <is>
-          <t>881370</t>
+          <t>000044</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>广告营销</t>
+          <t>上证中盘</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -13958,21 +13958,21 @@
     <row r="542">
       <c r="A542" s="1" t="inlineStr">
         <is>
-          <t>881373</t>
+          <t>000015</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>影视院线</t>
+          <t>红利指数</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -13983,21 +13983,21 @@
     <row r="543">
       <c r="A543" s="1" t="inlineStr">
         <is>
-          <t>881376</t>
+          <t>000019</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>数字媒体</t>
+          <t>治理指数</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -14008,21 +14008,21 @@
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
         <is>
-          <t>881380</t>
+          <t>000043</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>出版业</t>
+          <t>超大盘</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -14033,21 +14033,21 @@
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
         <is>
-          <t>881384</t>
+          <t>399330</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>广播电视</t>
+          <t>深证100</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -14058,21 +14058,21 @@
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
         <is>
-          <t>881386</t>
+          <t>399346</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>全国性银行</t>
+          <t>深证成长</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -14083,21 +14083,21 @@
     <row r="547">
       <c r="A547" s="1" t="inlineStr">
         <is>
-          <t>881389</t>
+          <t>399324</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>地方性银行</t>
+          <t>深证红利</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -14108,21 +14108,21 @@
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
         <is>
-          <t>881394</t>
+          <t>399328</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>深证治理</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -14133,21 +14133,21 @@
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
         <is>
-          <t>881395</t>
+          <t>399348</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>深证价值</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -14158,21 +14158,21 @@
     <row r="550">
       <c r="A550" s="1" t="inlineStr">
         <is>
-          <t>881396</t>
+          <t>399678</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>深次新股</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -14183,21 +14183,21 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>881406</t>
+          <t>399016</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>深证创新</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -14208,21 +14208,21 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>881407</t>
+          <t>399364</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>消费100</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -14233,21 +14233,21 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>881410</t>
+          <t>399319</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>资源优势</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -14258,21 +14258,21 @@
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>881415</t>
+          <t>399303</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>工程咨询服务</t>
+          <t>国证2000</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>42</v>
+        <v>2000</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -14283,21 +14283,21 @@
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
         <is>
-          <t>881416</t>
+          <t>399370</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>装修装饰</t>
+          <t>国证成长</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -14308,21 +14308,21 @@
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
         <is>
-          <t>881418</t>
+          <t>399371</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>国证价值</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>88</v>
+        <v>332</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -14333,21 +14333,21 @@
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
         <is>
-          <t>881422</t>
+          <t>399320</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>房产服务</t>
+          <t>国证服务</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -14358,21 +14358,21 @@
     <row r="558">
       <c r="A558" s="1" t="inlineStr">
         <is>
-          <t>881427</t>
+          <t>399321</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>体育</t>
+          <t>国证红利</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
     <row r="559">
       <c r="A559" s="1" t="inlineStr">
         <is>
-          <t>881428</t>
+          <t>399322</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>教育培训</t>
+          <t>国证治理</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
@@ -14408,21 +14408,21 @@
     <row r="560">
       <c r="A560" s="1" t="inlineStr">
         <is>
-          <t>881429</t>
+          <t>399359</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>酒店餐饮</t>
+          <t>国证基建</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
@@ -14433,21 +14433,21 @@
     <row r="561">
       <c r="A561" s="1" t="inlineStr">
         <is>
-          <t>881432</t>
+          <t>399365</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>旅游</t>
+          <t>国证粮食</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
     <row r="562">
       <c r="A562" s="1" t="inlineStr">
         <is>
-          <t>881436</t>
+          <t>399366</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>专业服务</t>
+          <t>能源金属</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
@@ -14483,21 +14483,21 @@
     <row r="563">
       <c r="A563" s="1" t="inlineStr">
         <is>
-          <t>881442</t>
+          <t>399363</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>公路铁路</t>
+          <t>国证算力</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
@@ -14508,21 +14508,21 @@
     <row r="564">
       <c r="A564" s="1" t="inlineStr">
         <is>
-          <t>881446</t>
+          <t>399362</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>航空机场</t>
+          <t>民企100</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
@@ -14533,21 +14533,21 @@
     <row r="565">
       <c r="A565" s="1" t="inlineStr">
         <is>
-          <t>881449</t>
+          <t>399361</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>航运港口</t>
+          <t>在线消费</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
@@ -14558,21 +14558,21 @@
     <row r="566">
       <c r="A566" s="1" t="inlineStr">
         <is>
-          <t>881452</t>
+          <t>399360</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>新硬件</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
@@ -14583,21 +14583,21 @@
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
         <is>
-          <t>881459</t>
+          <t>399608</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>科技100</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
@@ -14608,21 +14608,21 @@
     <row r="568">
       <c r="A568" s="1" t="inlineStr">
         <is>
-          <t>881467</t>
+          <t>399612</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>中创100</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
@@ -14633,21 +14633,21 @@
     <row r="569">
       <c r="A569" s="1" t="inlineStr">
         <is>
-          <t>881468</t>
+          <t>399550</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>央视50</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
@@ -14658,21 +14658,21 @@
     <row r="570">
       <c r="A570" s="1" t="inlineStr">
         <is>
-          <t>881470</t>
+          <t>000847</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>环保设备</t>
+          <t>腾讯济安</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="E570" t="inlineStr">
         <is>
@@ -14683,21 +14683,21 @@
     <row r="571">
       <c r="A571" s="1" t="inlineStr">
         <is>
-          <t>881471</t>
+          <t>399699</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>环境治理</t>
+          <t>金融科技</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
@@ -14708,21 +14708,21 @@
     <row r="572">
       <c r="A572" s="1" t="inlineStr">
         <is>
-          <t>881476</t>
+          <t>399391</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>环境监测</t>
+          <t>投资时钟</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E572" t="inlineStr">
         <is>
@@ -14733,21 +14733,21 @@
     <row r="573">
       <c r="A573" s="1" t="inlineStr">
         <is>
-          <t>881478</t>
+          <t>399286</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>综合类</t>
+          <t>区块链50</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
@@ -14758,12 +14758,12 @@
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
         <is>
-          <t>000300</t>
+          <t>000122</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>沪深300</t>
+          <t>农业主题</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="D574" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="E574" t="inlineStr">
         <is>
@@ -14783,12 +14783,12 @@
     <row r="575">
       <c r="A575" s="1" t="inlineStr">
         <is>
-          <t>399001</t>
+          <t>000698</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>深证成指</t>
+          <t>科创100</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="D575" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E575" t="inlineStr">
         <is>
@@ -14808,12 +14808,12 @@
     <row r="576">
       <c r="A576" s="1" t="inlineStr">
         <is>
-          <t>399006</t>
+          <t>000682</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>创业板指</t>
+          <t>科创信息</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -14822,7 +14822,7 @@
         </is>
       </c>
       <c r="D576" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
@@ -14833,12 +14833,12 @@
     <row r="577">
       <c r="A577" s="1" t="inlineStr">
         <is>
-          <t>399850</t>
+          <t>000683</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>深证50</t>
+          <t>科创生物</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -14858,12 +14858,12 @@
     <row r="578">
       <c r="A578" s="1" t="inlineStr">
         <is>
-          <t>000016</t>
+          <t>000685</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>上证50</t>
+          <t>科创芯片</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -14883,12 +14883,12 @@
     <row r="579">
       <c r="A579" s="1" t="inlineStr">
         <is>
-          <t>000688</t>
+          <t>000687</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>科创50</t>
+          <t>科创高装</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -14908,12 +14908,12 @@
     <row r="580">
       <c r="A580" s="1" t="inlineStr">
         <is>
-          <t>899050</t>
+          <t>000689</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>北证50</t>
+          <t>科创材料</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -14933,12 +14933,12 @@
     <row r="581">
       <c r="A581" s="1" t="inlineStr">
         <is>
-          <t>000903</t>
+          <t>000690</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>中证A100</t>
+          <t>科创成长</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="D581" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E581" t="inlineStr">
         <is>
@@ -14958,12 +14958,12 @@
     <row r="582">
       <c r="A582" s="1" t="inlineStr">
         <is>
-          <t>000510</t>
+          <t>399438</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>中证A500</t>
+          <t>绿色电力</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -14972,7 +14972,7 @@
         </is>
       </c>
       <c r="D582" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="E582" t="inlineStr">
         <is>
@@ -14983,12 +14983,12 @@
     <row r="583">
       <c r="A583" s="1" t="inlineStr">
         <is>
-          <t>000905</t>
+          <t>399974</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>中证500</t>
+          <t>国企改革</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="D583" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E583" t="inlineStr">
         <is>
@@ -15008,12 +15008,12 @@
     <row r="584">
       <c r="A584" s="1" t="inlineStr">
         <is>
-          <t>000906</t>
+          <t>399262</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>中证800</t>
+          <t>数字经济</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="D584" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="E584" t="inlineStr">
         <is>
@@ -15033,12 +15033,12 @@
     <row r="585">
       <c r="A585" s="1" t="inlineStr">
         <is>
-          <t>000852</t>
+          <t>399355</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>中证1000</t>
+          <t>长三角</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="D585" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="E585" t="inlineStr">
         <is>
@@ -15058,12 +15058,12 @@
     <row r="586">
       <c r="A586" s="1" t="inlineStr">
         <is>
-          <t>399750</t>
+          <t>399356</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>深主板50</t>
+          <t>珠三角</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -15072,7 +15072,7 @@
         </is>
       </c>
       <c r="D586" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
@@ -15083,12 +15083,12 @@
     <row r="587">
       <c r="A587" s="1" t="inlineStr">
         <is>
-          <t>399293</t>
+          <t>399357</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>创业大盘</t>
+          <t>环渤海</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -15097,7 +15097,7 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
@@ -15108,12 +15108,12 @@
     <row r="588">
       <c r="A588" s="1" t="inlineStr">
         <is>
-          <t>399673</t>
+          <t>399354</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>创业板50</t>
+          <t>分析师指数</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -15122,1634 +15122,9 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E588" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="1" t="inlineStr">
-        <is>
-          <t>399019</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>创业200</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D589" t="n">
-        <v>200</v>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" s="1" t="inlineStr">
-        <is>
-          <t>399012</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>创业300</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D590" t="n">
-        <v>298</v>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" s="1" t="inlineStr">
-        <is>
-          <t>399020</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>创业小盘</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D591" t="n">
-        <v>300</v>
-      </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" s="1" t="inlineStr">
-        <is>
-          <t>399018</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>创业创新</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D592" t="n">
-        <v>100</v>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="1" t="inlineStr">
-        <is>
-          <t>399295</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>创价值</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D593" t="n">
-        <v>50</v>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" s="1" t="inlineStr">
-        <is>
-          <t>399296</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>创成长</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D594" t="n">
-        <v>50</v>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" s="1" t="inlineStr">
-        <is>
-          <t>399269</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>创质量</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D595" t="n">
-        <v>100</v>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" s="1" t="inlineStr">
-        <is>
-          <t>399276</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>创科技</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D596" t="n">
-        <v>50</v>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" s="1" t="inlineStr">
-        <is>
-          <t>399275</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>创医药</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D597" t="n">
-        <v>50</v>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" s="1" t="inlineStr">
-        <is>
-          <t>399372</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>大盘成长</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D598" t="n">
-        <v>66</v>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" s="1" t="inlineStr">
-        <is>
-          <t>399373</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>大盘价值</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D599" t="n">
-        <v>66</v>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" s="1" t="inlineStr">
-        <is>
-          <t>399374</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>中盘成长</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D600" t="n">
-        <v>100</v>
-      </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" s="1" t="inlineStr">
-        <is>
-          <t>399375</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>中盘价值</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D601" t="n">
-        <v>100</v>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" s="1" t="inlineStr">
-        <is>
-          <t>399376</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>小盘成长</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D602" t="n">
-        <v>166</v>
-      </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="1" t="inlineStr">
-        <is>
-          <t>399377</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>小盘价值</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D603" t="n">
-        <v>166</v>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="1" t="inlineStr">
-        <is>
-          <t>000009</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>上证380</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D604" t="n">
-        <v>380</v>
-      </c>
-      <c r="E604" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" s="1" t="inlineStr">
-        <is>
-          <t>000010</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>上证180</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D605" t="n">
-        <v>180</v>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" s="1" t="inlineStr">
-        <is>
-          <t>000044</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>上证中盘</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D606" t="n">
-        <v>130</v>
-      </c>
-      <c r="E606" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" s="1" t="inlineStr">
-        <is>
-          <t>000015</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>红利指数</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D607" t="n">
-        <v>50</v>
-      </c>
-      <c r="E607" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" s="1" t="inlineStr">
-        <is>
-          <t>000019</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>治理指数</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D608" t="n">
-        <v>300</v>
-      </c>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" s="1" t="inlineStr">
-        <is>
-          <t>000043</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>超大盘</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D609" t="n">
-        <v>20</v>
-      </c>
-      <c r="E609" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" s="1" t="inlineStr">
-        <is>
-          <t>399330</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>深证100</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D610" t="n">
-        <v>100</v>
-      </c>
-      <c r="E610" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" s="1" t="inlineStr">
-        <is>
-          <t>399346</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>深证成长</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D611" t="n">
-        <v>100</v>
-      </c>
-      <c r="E611" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" s="1" t="inlineStr">
-        <is>
-          <t>399324</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>深证红利</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D612" t="n">
-        <v>40</v>
-      </c>
-      <c r="E612" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="1" t="inlineStr">
-        <is>
-          <t>399328</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>深证治理</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D613" t="n">
-        <v>40</v>
-      </c>
-      <c r="E613" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" s="1" t="inlineStr">
-        <is>
-          <t>399348</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>深证价值</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D614" t="n">
-        <v>100</v>
-      </c>
-      <c r="E614" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="1" t="inlineStr">
-        <is>
-          <t>399678</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>深次新股</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D615" t="n">
-        <v>100</v>
-      </c>
-      <c r="E615" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" s="1" t="inlineStr">
-        <is>
-          <t>399016</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>深证创新</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D616" t="n">
-        <v>100</v>
-      </c>
-      <c r="E616" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" s="1" t="inlineStr">
-        <is>
-          <t>399364</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>消费100</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D617" t="n">
-        <v>100</v>
-      </c>
-      <c r="E617" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" s="1" t="inlineStr">
-        <is>
-          <t>399319</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>资源优势</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D618" t="n">
-        <v>100</v>
-      </c>
-      <c r="E618" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" s="1" t="inlineStr">
-        <is>
-          <t>399303</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>国证2000</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D619" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" s="1" t="inlineStr">
-        <is>
-          <t>399370</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>国证成长</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D620" t="n">
-        <v>332</v>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" s="1" t="inlineStr">
-        <is>
-          <t>399371</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>国证价值</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D621" t="n">
-        <v>332</v>
-      </c>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" s="1" t="inlineStr">
-        <is>
-          <t>399320</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>国证服务</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D622" t="n">
-        <v>100</v>
-      </c>
-      <c r="E622" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" s="1" t="inlineStr">
-        <is>
-          <t>399321</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>国证红利</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D623" t="n">
-        <v>50</v>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" s="1" t="inlineStr">
-        <is>
-          <t>399322</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>国证治理</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D624" t="n">
-        <v>50</v>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" s="1" t="inlineStr">
-        <is>
-          <t>399359</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>国证基建</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D625" t="n">
-        <v>50</v>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" s="1" t="inlineStr">
-        <is>
-          <t>399365</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>国证粮食</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D626" t="n">
-        <v>50</v>
-      </c>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" s="1" t="inlineStr">
-        <is>
-          <t>399366</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>能源金属</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D627" t="n">
-        <v>49</v>
-      </c>
-      <c r="E627" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" s="1" t="inlineStr">
-        <is>
-          <t>399363</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>国证算力</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D628" t="n">
-        <v>50</v>
-      </c>
-      <c r="E628" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" s="1" t="inlineStr">
-        <is>
-          <t>399362</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>民企100</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D629" t="n">
-        <v>100</v>
-      </c>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" s="1" t="inlineStr">
-        <is>
-          <t>399361</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>在线消费</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D630" t="n">
-        <v>50</v>
-      </c>
-      <c r="E630" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" s="1" t="inlineStr">
-        <is>
-          <t>399360</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>新硬件</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D631" t="n">
-        <v>100</v>
-      </c>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" s="1" t="inlineStr">
-        <is>
-          <t>399608</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>科技100</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D632" t="n">
-        <v>100</v>
-      </c>
-      <c r="E632" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" s="1" t="inlineStr">
-        <is>
-          <t>399612</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>中创100</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D633" t="n">
-        <v>100</v>
-      </c>
-      <c r="E633" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" s="1" t="inlineStr">
-        <is>
-          <t>399550</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>央视50</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D634" t="n">
-        <v>50</v>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" s="1" t="inlineStr">
-        <is>
-          <t>000847</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>腾讯济安</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D635" t="n">
-        <v>100</v>
-      </c>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" s="1" t="inlineStr">
-        <is>
-          <t>399699</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>金融科技</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D636" t="n">
-        <v>57</v>
-      </c>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" s="1" t="inlineStr">
-        <is>
-          <t>399391</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>投资时钟</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D637" t="n">
-        <v>100</v>
-      </c>
-      <c r="E637" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" s="1" t="inlineStr">
-        <is>
-          <t>399286</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>区块链50</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D638" t="n">
-        <v>49</v>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" s="1" t="inlineStr">
-        <is>
-          <t>000122</t>
-        </is>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>农业主题</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D639" t="n">
-        <v>50</v>
-      </c>
-      <c r="E639" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" s="1" t="inlineStr">
-        <is>
-          <t>000698</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>科创100</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D640" t="n">
-        <v>100</v>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" s="1" t="inlineStr">
-        <is>
-          <t>000682</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>科创信息</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D641" t="n">
-        <v>50</v>
-      </c>
-      <c r="E641" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" s="1" t="inlineStr">
-        <is>
-          <t>000683</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>科创生物</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D642" t="n">
-        <v>50</v>
-      </c>
-      <c r="E642" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" s="1" t="inlineStr">
-        <is>
-          <t>000685</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>科创芯片</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D643" t="n">
-        <v>50</v>
-      </c>
-      <c r="E643" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" s="1" t="inlineStr">
-        <is>
-          <t>000687</t>
-        </is>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>科创高装</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D644" t="n">
-        <v>50</v>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" s="1" t="inlineStr">
-        <is>
-          <t>000689</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>科创材料</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D645" t="n">
-        <v>50</v>
-      </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" s="1" t="inlineStr">
-        <is>
-          <t>000690</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>科创成长</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D646" t="n">
-        <v>50</v>
-      </c>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" s="1" t="inlineStr">
-        <is>
-          <t>399438</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>绿色电力</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D647" t="n">
-        <v>50</v>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" s="1" t="inlineStr">
-        <is>
-          <t>399974</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>国企改革</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D648" t="n">
-        <v>100</v>
-      </c>
-      <c r="E648" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" s="1" t="inlineStr">
-        <is>
-          <t>399262</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>数字经济</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D649" t="n">
-        <v>50</v>
-      </c>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" s="1" t="inlineStr">
-        <is>
-          <t>399355</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>长三角</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D650" t="n">
-        <v>40</v>
-      </c>
-      <c r="E650" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" s="1" t="inlineStr">
-        <is>
-          <t>399356</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>珠三角</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D651" t="n">
-        <v>40</v>
-      </c>
-      <c r="E651" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" s="1" t="inlineStr">
-        <is>
-          <t>399357</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>环渤海</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D652" t="n">
-        <v>40</v>
-      </c>
-      <c r="E652" t="inlineStr">
-        <is>
-          <t>TDXBLK</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" s="1" t="inlineStr">
-        <is>
-          <t>399354</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>分析师指数</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>指数</t>
-        </is>
-      </c>
-      <c r="D653" t="n">
-        <v>99</v>
-      </c>
-      <c r="E653" t="inlineStr">
         <is>
           <t>TDXBLK</t>
         </is>

--- a/TDXapp/tdxAppData/tdxIndexsBLK.xlsx
+++ b/TDXapp/tdxAppData/tdxIndexsBLK.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="20745" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3117,7 +3117,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3128,13 +3128,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3602,28 +3595,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3632,118 +3628,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4101,6 +4094,11 @@
   <dimension ref="A1:F508"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="5.375" customWidth="1"/>
+    <col min="5" max="5" width="7.375" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
